--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3149-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3149-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DA56B4A-CDA9-4371-B3EF-D119112E08AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E140046-C936-45F5-98BD-766CA3211000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{93B6218A-3B07-4945-89BD-A28872962BDE}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{A6CCB23C-3723-46F2-85A0-0FF1FBE40E83}"/>
   </bookViews>
   <sheets>
     <sheet name="3149-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1466,24 +1466,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7BE1796-77F2-4687-A5C7-52151019AF73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6A016CB-8E46-4E67-A2EC-6C3D1C4B4CA6}">
   <dimension ref="A1:R45"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="5.109375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.5546875" customWidth="1"/>
+    <col min="1" max="2" width="6.5" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1511,7 +1511,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1541,7 +1541,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2023,7 +2023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2020</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2019</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>25</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>25</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2018</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2017</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2016</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2015</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2014</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2013</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2012</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2011</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2010</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2009</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2008</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2007</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2006</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2005</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2004</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2003</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2001</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>2000</v>
       </c>
@@ -3771,7 +3771,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>1999</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37" t="s">
         <v>41</v>
       </c>
